--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487106_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487106_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3328</v>
+        <v>4.8068</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7231</v>
+        <v>3.9828</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6098</v>
+        <v>0.8239</v>
       </c>
       <c r="G2" t="n">
         <v>2.0999</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8672</v>
+        <v>-0.3933</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8328</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0344</v>
+        <v>0.1798</v>
       </c>
       <c r="V2" t="n">
         <v>1.5561</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3473</v>
+        <v>2.0449</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3169</v>
+        <v>2.3357</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0305</v>
+        <v>-0.2908</v>
       </c>
       <c r="G3" t="n">
         <v>1.9364</v>
@@ -688,13 +688,13 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5883</v>
+        <v>0.2859</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0462</v>
+        <v>-0.0274</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6345</v>
+        <v>0.3133</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3704</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6621</v>
+        <v>1.4078</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2577</v>
+        <v>2.5509</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4044</v>
+        <v>-1.1432</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1539</v>
+        <v>0.0504</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2038</v>
+        <v>2.0968</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3577</v>
+        <v>-2.0464</v>
       </c>
       <c r="J4" t="n">
-        <v>1.494</v>
+        <v>1.7053</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4126</v>
+        <v>3.586</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0814</v>
+        <v>-1.8807</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6479</v>
+        <v>-1.6549</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2087</v>
+        <v>-1.4892</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4391</v>
+        <v>-0.1657</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.193</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R4" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7232</v>
+        <v>0.8315</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4429</v>
+        <v>0.0569</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2803</v>
+        <v>0.7746</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2859</v>
+        <v>2.4559</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2859</v>
+        <v>3.6839</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1143</v>
+        <v>1.1793</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1503</v>
+        <v>1.1764</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0361</v>
+        <v>0.0029</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0504</v>
+        <v>-0.1539</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0968</v>
+        <v>0.2038</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0464</v>
+        <v>-0.3577</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7053</v>
+        <v>1.494</v>
       </c>
       <c r="K5" t="n">
-        <v>3.586</v>
+        <v>1.4126</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.8807</v>
+        <v>0.0814</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6549</v>
+        <v>-1.6479</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4892</v>
+        <v>-1.2087</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1657</v>
+        <v>-0.4391</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>0.538</v>
+        <v>1.2403</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3437</v>
+        <v>0.3616</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8817</v>
+        <v>0.8787</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4559</v>
+        <v>0.2859</v>
       </c>
       <c r="W5" t="n">
-        <v>3.6839</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.606</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2257</v>
+        <v>1.3853</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7504</v>
+        <v>-1.9913</v>
       </c>
       <c r="G7" t="n">
         <v>0.6899</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1448</v>
+        <v>-0.2261</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8328</v>
+        <v>-0.6732</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6881</v>
+        <v>0.4471</v>
       </c>
       <c r="V7" t="n">
         <v>-1.842</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3824</v>
+        <v>-1.6095</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1416</v>
+        <v>-2.5829</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7592</v>
+        <v>0.9734</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7023</v>
@@ -1078,13 +1078,13 @@
         <v>1.5441</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3199</v>
+        <v>0.0929</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3239</v>
+        <v>-0.1173</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.004</v>
+        <v>0.2102</v>
       </c>
       <c r="V8" t="n">
         <v>-0.614</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9388</v>
+        <v>-2.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4545</v>
+        <v>-0.4279</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3933</v>
+        <v>-2.0721</v>
       </c>
       <c r="G9" t="n">
         <v>0.0238</v>
@@ -1156,13 +1156,13 @@
         <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>2.0676</v>
+        <v>1.5064</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9566</v>
+        <v>1.0741</v>
       </c>
       <c r="U9" t="n">
-        <v>0.111</v>
+        <v>0.4323</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9421</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6827</v>
+        <v>-3.5964</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4224</v>
+        <v>-0.3629</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2604</v>
+        <v>-3.2336</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8152</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6977</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4297</v>
+        <v>0.4891</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1818</v>
+        <v>0.2085</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5138</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.274</v>
+        <v>-3.7491</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4597</v>
+        <v>-0.8012</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8143</v>
+        <v>-2.9479</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3634</v>
+        <v>-1.8613</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5837</v>
+        <v>-0.1469</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-1.7144</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0887</v>
+        <v>0.4542</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5382</v>
+        <v>1.1953</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6269</v>
+        <v>-0.7411</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2747</v>
+        <v>-2.3155</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1219</v>
+        <v>-1.3423</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1528</v>
+        <v>-0.9732</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1231</v>
+        <v>-0.579</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5017</v>
+        <v>0.5754</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4759</v>
+        <v>0.3659</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0258</v>
+        <v>0.2095</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2859</v>
+        <v>-1.8842</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0371</v>
+        <v>-3.8685</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8214</v>
+        <v>-3.081</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2156</v>
+        <v>-0.7875</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8613</v>
+        <v>-1.3634</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1469</v>
+        <v>-0.5837</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7144</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4542</v>
+        <v>-0.0887</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1953</v>
+        <v>0.5382</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7411</v>
+        <v>-0.6269</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3155</v>
+        <v>-1.2747</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3423</v>
+        <v>-1.1219</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9732</v>
+        <v>-0.1528</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.579</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R12" t="n">
-        <v>0.386</v>
+        <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7125</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6544</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0582</v>
+        <v>0.001</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8842</v>
+        <v>-0.2859</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.309200000000002</v>
+        <v>-6.416699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2236</v>
+        <v>4.1157</v>
       </c>
       <c r="F13" t="n">
         <v>-10.5327</v>
@@ -1465,19 +1465,19 @@
         <v>-15.4405</v>
       </c>
       <c r="R13" t="n">
-        <v>8.685199999999998</v>
+        <v>8.6852</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5627</v>
+        <v>4.455000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.09220000000000017</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>3.655</v>
+        <v>3.654999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.154500000000001</v>
+        <v>-3.1545</v>
       </c>
       <c r="W13" t="n">
         <v>5.071099999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.927899999999999</v>
+        <v>9.6196</v>
       </c>
       <c r="E14" t="n">
-        <v>9.105600000000001</v>
+        <v>9.305899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8223</v>
+        <v>0.3137</v>
       </c>
       <c r="G14" t="n">
         <v>7.6056</v>
@@ -1546,13 +1546,13 @@
         <v>3.0881</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1289</v>
+        <v>-0.4373</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8791</v>
+        <v>-0.6788</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7502</v>
+        <v>0.2415</v>
       </c>
       <c r="V14" t="n">
         <v>0.3281</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1194</v>
+        <v>2.4396</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0672</v>
+        <v>2.4678</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0522</v>
+        <v>-0.0282</v>
       </c>
       <c r="G15" t="n">
         <v>-0.09</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0331</v>
+        <v>-0.7129</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8328</v>
+        <v>-0.4323</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2003</v>
+        <v>-0.2806</v>
       </c>
       <c r="V15" t="n">
         <v>1.3125</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7607</v>
+        <v>1.2426</v>
       </c>
       <c r="E16" t="n">
         <v>-0.515</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2758</v>
+        <v>1.7576</v>
       </c>
       <c r="G16" t="n">
         <v>1.5843</v>
@@ -1702,13 +1702,13 @@
         <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6306</v>
+        <v>-0.1487</v>
       </c>
       <c r="T16" t="n">
         <v>-0.4032</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2274</v>
+        <v>0.2545</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. ELKSNIS</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2759</v>
+        <v>0.6383</v>
       </c>
       <c r="E17" t="n">
-        <v>1.54</v>
+        <v>3.5295</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2641</v>
+        <v>-2.8912</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9238</v>
+        <v>0.05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6035</v>
+        <v>2.4034</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5273</v>
+        <v>-2.3534</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2406</v>
+        <v>2.7002</v>
       </c>
       <c r="K17" t="n">
-        <v>3.348</v>
+        <v>4.7608</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1074</v>
+        <v>-2.0606</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1644</v>
+        <v>-2.6502</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.7446</v>
+        <v>-2.3574</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4199</v>
+        <v>-0.2928</v>
       </c>
       <c r="P17" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9301</v>
+        <v>2.7021</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2346</v>
+        <v>-1.1065</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2644</v>
+        <v>-0.6193</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0298</v>
+        <v>-0.4872</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4137</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1253</v>
+        <v>0.1521</v>
       </c>
       <c r="E18" t="n">
         <v>0.0019</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1234</v>
+        <v>0.1502</v>
       </c>
       <c r="G18" t="n">
         <v>0.048</v>
@@ -1858,13 +1858,13 @@
         <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0562</v>
+        <v>-0.0294</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>R. ELKSNIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0438</v>
+        <v>-0.6194</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3293</v>
+        <v>0.9392</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.373</v>
+        <v>-1.5586</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05</v>
+        <v>-0.9238</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4034</v>
+        <v>0.6035</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.3534</v>
+        <v>-1.5273</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7002</v>
+        <v>2.2406</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7608</v>
+        <v>3.348</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0606</v>
+        <v>-1.1074</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6502</v>
+        <v>-3.1644</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.3574</v>
+        <v>-2.7446</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2928</v>
+        <v>-0.4199</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7021</v>
+        <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7886</v>
+        <v>-0.6607</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8196</v>
+        <v>-0.3364</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.969</v>
+        <v>-0.3242</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4137</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9223</v>
+        <v>-0.8955</v>
       </c>
       <c r="E20" t="n">
         <v>-0.6457000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2766</v>
+        <v>-0.2498</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8066</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0562</v>
+        <v>-0.0294</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4362</v>
+        <v>-1.2619</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2075</v>
+        <v>-1.5542</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7713</v>
+        <v>0.2924</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3164</v>
+        <v>-3.4001</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6177</v>
+        <v>-3.4051</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3013</v>
+        <v>0.005</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1962</v>
+        <v>-1.4042</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2369</v>
+        <v>-1.4285</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0407</v>
+        <v>0.0243</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1202</v>
+        <v>-1.996</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3808</v>
+        <v>-1.9767</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2606</v>
+        <v>-0.0193</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>-0.965</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R21" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>1.394</v>
+        <v>-0.2525</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0462</v>
+        <v>-0.6107</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4403</v>
+        <v>0.3582</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5138</v>
+        <v>3.3558</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.3558</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.514</v>
+        <v>-1.7073</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1882</v>
+        <v>-0.4886</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3258</v>
+        <v>-1.2187</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7887</v>
@@ -2170,13 +2170,13 @@
         <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4045</v>
+        <v>-0.5979</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1917</v>
+        <v>-0.1087</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5962</v>
+        <v>-0.4891</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2859</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9837</v>
+        <v>-2.2988</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9548</v>
+        <v>-2.508</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0289</v>
+        <v>0.2091</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4001</v>
+        <v>-1.3164</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.4051</v>
+        <v>-1.6177</v>
       </c>
       <c r="I23" t="n">
-        <v>0.005</v>
+        <v>0.3013</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4042</v>
+        <v>-1.1962</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4285</v>
+        <v>-1.2369</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0243</v>
+        <v>0.0407</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.996</v>
+        <v>-0.1202</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9767</v>
+        <v>-0.3808</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0193</v>
+        <v>0.2606</v>
       </c>
       <c r="P23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9743000000000001</v>
+        <v>0.5314</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0113</v>
+        <v>-0.3467</v>
       </c>
       <c r="U23" t="n">
-        <v>0.037</v>
+        <v>0.8781</v>
       </c>
       <c r="V23" t="n">
-        <v>3.3558</v>
+        <v>-1.5138</v>
       </c>
       <c r="W23" t="n">
-        <v>3.3558</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.309200000000001</v>
+        <v>7.3093</v>
       </c>
       <c r="E24" t="n">
         <v>10.5328</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2234</v>
+        <v>-3.2235</v>
       </c>
       <c r="G24" t="n">
-        <v>0.962299999999999</v>
+        <v>0.962300000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-0.5015000000000001</v>
@@ -2317,7 +2317,7 @@
         <v>-0.1288000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>6.755300000000001</v>
+        <v>6.7553</v>
       </c>
       <c r="Q24" t="n">
         <v>-8.6852</v>
@@ -2326,22 +2326,22 @@
         <v>15.4406</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.5628</v>
+        <v>-3.5629</v>
       </c>
       <c r="T24" t="n">
         <v>-3.6551</v>
       </c>
       <c r="U24" t="n">
-        <v>0.09240000000000001</v>
+        <v>0.09240000000000004</v>
       </c>
       <c r="V24" t="n">
-        <v>3.1545</v>
+        <v>3.154500000000001</v>
       </c>
       <c r="W24" t="n">
         <v>8.2255</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.071000000000001</v>
+        <v>-5.071</v>
       </c>
     </row>
   </sheetData>
